--- a/04 Ressourcen/Mathematik/Stoffverteilungsplan 26-27 Mathe 10.xlsx
+++ b/04 Ressourcen/Mathematik/Stoffverteilungsplan 26-27 Mathe 10.xlsx
@@ -598,25 +598,11 @@
       <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>19.10</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>23.10</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Zeitfenster</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Berlinfahrt der 10er 19.10.-23.10. (kein Unterricht, Woche 6 mit Zeitfenster entfällt)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1390,12 +1376,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
